--- a/luban-excels/xlsx/__enums__ - 副本.xlsx
+++ b/luban-excels/xlsx/__enums__ - 副本.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="183">
   <si>
     <t>##var</t>
   </si>
@@ -329,6 +329,15 @@
     <t>狗狗的各种状态枚举</t>
   </si>
   <si>
+    <t>Bespoke</t>
+  </si>
+  <si>
+    <t>特殊处理</t>
+  </si>
+  <si>
+    <t>特殊处理的方式需要和开发人员约定来定制</t>
+  </si>
+  <si>
     <t>Default</t>
   </si>
   <si>
@@ -386,25 +395,46 @@
     <t>等待下注时</t>
   </si>
   <si>
+    <t>Dealt</t>
+  </si>
+  <si>
     <t>等待玩家选牌</t>
   </si>
   <si>
+    <t>WaitingForHint</t>
+  </si>
+  <si>
     <t>玩家选牌中等待询问时</t>
   </si>
   <si>
+    <t>HintResult</t>
+  </si>
+  <si>
     <t>展示询问结果</t>
   </si>
   <si>
+    <t>HintExhausted</t>
+  </si>
+  <si>
     <t>询问机会用尽</t>
   </si>
   <si>
     <t>得到询问结果后，玩家又更改了选牌</t>
   </si>
   <si>
+    <t>RefuseHint</t>
+  </si>
+  <si>
     <t>拒绝询问</t>
   </si>
   <si>
+    <t>Drawing</t>
+  </si>
+  <si>
     <t>补牌中</t>
+  </si>
+  <si>
+    <t>Settled</t>
   </si>
   <si>
     <t>看到结算结果</t>
@@ -1194,7 +1224,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1215,9 +1245,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2162,7 +2189,7 @@
         <v>101</v>
       </c>
       <c r="J33" s="1">
-        <v>1001</v>
+        <v>2</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>102</v>
@@ -2176,264 +2203,295 @@
         <v>104</v>
       </c>
       <c r="J34" s="1">
-        <v>1002</v>
+        <v>1001</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="H35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J36" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="H37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J37" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="H38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J38" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="H39" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J39" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="40" spans="2:11">
       <c r="H40" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J40" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="H41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J41" s="1">
         <v>1008</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
-      <c r="H41" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="J41" s="7">
+    <row r="42" spans="2:11">
+      <c r="H42" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="J42" s="5">
         <v>2001</v>
       </c>
     </row>
-    <row r="42" spans="2:11">
-      <c r="H42" s="7"/>
-      <c r="I42" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J42" s="7">
+    <row r="43" spans="2:11">
+      <c r="H43" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J43" s="5">
         <v>2002</v>
       </c>
     </row>
-    <row r="43" spans="2:11">
-      <c r="H43" s="7"/>
-      <c r="I43" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="J43" s="7">
+    <row r="44" spans="2:11">
+      <c r="H44" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J44" s="5">
         <v>2003</v>
       </c>
     </row>
-    <row r="44" spans="2:11">
-      <c r="I44" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J44" s="7">
+    <row r="45" spans="2:11">
+      <c r="H45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45" s="5">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="H46" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J46" s="5">
         <v>2005</v>
       </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="I45" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J45" s="7">
+      <c r="K46" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="H47" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J47" s="5">
         <v>2006</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="I46" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J46" s="7">
+    </row>
+    <row r="48" spans="2:11">
+      <c r="H48" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J48" s="5">
         <v>2007</v>
       </c>
     </row>
-    <row r="47" spans="2:11">
-      <c r="H47" s="7"/>
-      <c r="I47" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J47" s="7">
+    <row r="49" spans="8:10">
+      <c r="H49" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J49" s="5">
         <v>2008</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="H48" s="7"/>
-      <c r="I48" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48" s="7">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="49" spans="8:10">
-      <c r="H49" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J49" s="1">
-        <v>3001</v>
       </c>
     </row>
     <row r="50" spans="8:10">
       <c r="H50" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="J50" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="51" spans="8:10">
       <c r="H51" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J51" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="52" spans="8:10">
       <c r="H52" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J52" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="53" spans="8:10">
       <c r="H53" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="J53" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="54" spans="8:10">
       <c r="H54" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J54" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="55" spans="8:10">
       <c r="H55" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J55" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="56" spans="8:10">
       <c r="H56" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J56" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="57" spans="8:10">
       <c r="H57" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J57" s="1">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="58" spans="8:10">
       <c r="H58" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J58" s="1">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="59" spans="8:10">
+      <c r="H59" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="1">
         <v>3010</v>
       </c>
     </row>
     <row r="65" spans="2:10">
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C65" s="5" t="b">
         <v>0</v>
@@ -2442,13 +2500,13 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="J65" s="1">
         <v>1</v>
@@ -2456,10 +2514,10 @@
     </row>
     <row r="66" spans="2:10">
       <c r="H66" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="J66" s="1">
         <v>2</v>
@@ -2467,10 +2525,10 @@
     </row>
     <row r="67" spans="2:10">
       <c r="H67" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J67" s="1">
         <v>3</v>
@@ -2480,10 +2538,10 @@
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="H68" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="J68" s="1">
         <v>4</v>
@@ -2491,10 +2549,10 @@
     </row>
     <row r="69" spans="2:10">
       <c r="H69" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -2502,10 +2560,10 @@
     </row>
     <row r="70" spans="2:10">
       <c r="H70" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J70" s="1">
         <v>6</v>
@@ -2513,10 +2571,10 @@
     </row>
     <row r="71" spans="2:10">
       <c r="H71" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="J71" s="1">
         <v>7</v>
@@ -2524,10 +2582,10 @@
     </row>
     <row r="72" spans="2:10">
       <c r="H72" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J72" s="1">
         <v>8</v>
@@ -2537,10 +2595,10 @@
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="H73" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="J73" s="1">
         <v>9</v>
@@ -2548,10 +2606,10 @@
     </row>
     <row r="74" spans="2:10">
       <c r="H74" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="J74" s="1">
         <v>10</v>
@@ -2559,7 +2617,7 @@
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C98" s="5" t="b">
         <v>0</v>
@@ -2568,20 +2626,20 @@
         <v>1</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="H99" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="H100" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="111" spans="2:9">

--- a/luban-excels/xlsx/__enums__ - 副本.xlsx
+++ b/luban-excels/xlsx/__enums__ - 副本.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="184">
   <si>
     <t>##var</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>狗狗的各种状态枚举</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>Bespoke</t>
@@ -2185,313 +2188,321 @@
       <c r="H33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="J33" s="1">
-        <v>2</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:11">
       <c r="H34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1001</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="H35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1001</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1002</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="J36" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="H37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="J37" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="H38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="J38" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="H39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="J39" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="40" spans="2:11">
       <c r="H40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="J40" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="41" spans="2:11">
       <c r="H41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="J41" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="H42" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J41" s="1">
+      <c r="I42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J42" s="1">
         <v>1008</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="H42" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="5">
-        <v>2001</v>
       </c>
     </row>
     <row r="43" spans="2:11">
       <c r="H43" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="J43" s="5">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="44" spans="2:11">
       <c r="H44" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="J44" s="5">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="H45" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="J44" s="5">
+      <c r="I45" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J45" s="5">
         <v>2003</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="H45" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J45" s="5">
-        <v>2004</v>
       </c>
     </row>
     <row r="46" spans="2:11">
       <c r="H46" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="J46" s="5">
-        <v>2005</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>130</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="47" spans="2:11">
       <c r="H47" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J47" s="5">
+        <v>2005</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I47" s="1" t="s">
+    </row>
+    <row r="48" spans="2:11">
+      <c r="H48" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J47" s="5">
+      <c r="I48" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J48" s="5">
         <v>2006</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="H48" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J48" s="5">
-        <v>2007</v>
       </c>
     </row>
     <row r="49" spans="8:10">
       <c r="H49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="J49" s="5">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="50" spans="8:10">
+      <c r="H50" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J49" s="5">
+      <c r="I50" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J50" s="5">
         <v>2008</v>
-      </c>
-    </row>
-    <row r="50" spans="8:10">
-      <c r="H50" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J50" s="1">
-        <v>3001</v>
       </c>
     </row>
     <row r="51" spans="8:10">
       <c r="H51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="J51" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="52" spans="8:10">
       <c r="H52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="J52" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="53" spans="8:10">
       <c r="H53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="J53" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="54" spans="8:10">
       <c r="H54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="J54" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="55" spans="8:10">
       <c r="H55" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J55" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="56" spans="8:10">
       <c r="H56" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J56" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="57" spans="8:10">
       <c r="H57" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="J57" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="58" spans="8:10">
       <c r="H58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="J58" s="1">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="59" spans="8:10">
       <c r="H59" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="J59" s="1">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="60" spans="8:10">
+      <c r="H60" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J59" s="1">
+      <c r="I60" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J60" s="1">
         <v>3010</v>
       </c>
     </row>
     <row r="65" spans="2:10">
       <c r="B65" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C65" s="5" t="b">
         <v>0</v>
@@ -2500,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J65" s="1">
         <v>1</v>
@@ -2514,10 +2525,10 @@
     </row>
     <row r="66" spans="2:10">
       <c r="H66" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J66" s="1">
         <v>2</v>
@@ -2525,10 +2536,10 @@
     </row>
     <row r="67" spans="2:10">
       <c r="H67" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J67" s="1">
         <v>3</v>
@@ -2538,10 +2549,10 @@
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="H68" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J68" s="1">
         <v>4</v>
@@ -2549,10 +2560,10 @@
     </row>
     <row r="69" spans="2:10">
       <c r="H69" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -2560,10 +2571,10 @@
     </row>
     <row r="70" spans="2:10">
       <c r="H70" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J70" s="1">
         <v>6</v>
@@ -2571,10 +2582,10 @@
     </row>
     <row r="71" spans="2:10">
       <c r="H71" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J71" s="1">
         <v>7</v>
@@ -2582,10 +2593,10 @@
     </row>
     <row r="72" spans="2:10">
       <c r="H72" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J72" s="1">
         <v>8</v>
@@ -2595,10 +2606,10 @@
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="H73" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J73" s="1">
         <v>9</v>
@@ -2606,10 +2617,10 @@
     </row>
     <row r="74" spans="2:10">
       <c r="H74" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J74" s="1">
         <v>10</v>
@@ -2617,7 +2628,7 @@
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C98" s="5" t="b">
         <v>0</v>
@@ -2626,20 +2637,20 @@
         <v>1</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="99" spans="2:9">
       <c r="H99" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="H100" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="2:9">

--- a/luban-excels/xlsx/__enums__ - 副本.xlsx
+++ b/luban-excels/xlsx/__enums__ - 副本.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="216">
   <si>
     <t>##var</t>
   </si>
@@ -164,6 +164,12 @@
     <t>卡面</t>
   </si>
   <si>
+    <t>Refreshment</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
     <t>ERarity</t>
   </si>
   <si>
@@ -567,6 +573,96 @@
   </si>
   <si>
     <t>皇家同花顺</t>
+  </si>
+  <si>
+    <t>EAcquisitionType</t>
+  </si>
+  <si>
+    <t>投放类型</t>
+  </si>
+  <si>
+    <t>Initial</t>
+  </si>
+  <si>
+    <t>初始拥有</t>
+  </si>
+  <si>
+    <t>DecorationBlindBox</t>
+  </si>
+  <si>
+    <t>装扮盲盒产出</t>
+  </si>
+  <si>
+    <t>RefreshmentBlindBox</t>
+  </si>
+  <si>
+    <t>消耗品盲盒产出</t>
+  </si>
+  <si>
+    <t>EventReward</t>
+  </si>
+  <si>
+    <t>活动产出</t>
+  </si>
+  <si>
+    <t>活动/LinkTree等</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>已下架</t>
+  </si>
+  <si>
+    <t>DebugOnly</t>
+  </si>
+  <si>
+    <t>仅调试</t>
+  </si>
+  <si>
+    <t>EBlindBoxType</t>
+  </si>
+  <si>
+    <t>盲盒类型</t>
+  </si>
+  <si>
+    <t>Decoration</t>
+  </si>
+  <si>
+    <t>装扮盲盒</t>
+  </si>
+  <si>
+    <t>NewbieDecoration</t>
+  </si>
+  <si>
+    <t>新手装扮盲盒</t>
+  </si>
+  <si>
+    <t>消耗品盲盒</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>活动盲盒</t>
+  </si>
+  <si>
+    <t>枚举名字策划请不要轻易改，跟开发人员约定后面加BoxWeight对应Item表的权重</t>
+  </si>
+  <si>
+    <t>EBlindBoxDisplayMode</t>
+  </si>
+  <si>
+    <t>RevealUpgrade</t>
+  </si>
+  <si>
+    <t>三次升级表演</t>
+  </si>
+  <si>
+    <t>DirectReward</t>
+  </si>
+  <si>
+    <t>直接展示奖励</t>
   </si>
   <si>
     <t>EEnumType</t>
@@ -1568,7 +1664,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="9.66666666666667" style="1" customWidth="1"/>
@@ -1904,29 +2000,36 @@
       <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="5" t="b">
+      <c r="I15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="b">
+      <c r="D16" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
       <c r="H16" s="1" t="s">
         <v>49</v>
       </c>
@@ -1934,11 +2037,10 @@
         <v>50</v>
       </c>
       <c r="J16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" ht="18" spans="1:11">
-      <c r="A17" s="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="H17" s="1" t="s">
         <v>51</v>
       </c>
@@ -1946,10 +2048,11 @@
         <v>52</v>
       </c>
       <c r="J17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:11">
+      <c r="A18" s="6"/>
       <c r="H18" s="1" t="s">
         <v>53</v>
       </c>
@@ -1957,7 +2060,7 @@
         <v>54</v>
       </c>
       <c r="J18" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1968,267 +2071,267 @@
         <v>56</v>
       </c>
       <c r="J19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="H20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="1">
         <v>5</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="H20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J20" s="1">
+    </row>
+    <row r="21" spans="1:11">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="H21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" s="1">
         <v>6</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="B21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="5" t="b">
+      <c r="K21" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="B22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="5" t="b">
+      <c r="D22" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J21" s="1">
+      <c r="H22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J22" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="H22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="J22" s="1">
-        <v>2</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="H23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="J23" s="1">
-        <v>4</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="H24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1">
+        <v>4</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J24" s="1">
+    </row>
+    <row r="25" spans="1:11">
+      <c r="H25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="1">
         <v>8</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="H25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="1">
+    </row>
+    <row r="26" spans="1:11">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="H26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J26" s="1">
         <v>16</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="H26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="J26" s="1">
-        <v>32</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="H27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1">
+        <v>32</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="J27" s="1">
-        <v>64</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="H28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1">
+        <v>64</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="J28" s="1">
-        <v>128</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="H29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1">
+        <v>128</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="J29" s="1">
+    </row>
+    <row r="30" spans="1:11">
+      <c r="H30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" s="1">
         <v>256</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="H30" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="5" t="s">
+      <c r="K30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J30" s="1">
+    </row>
+    <row r="31" spans="1:11">
+      <c r="H31" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="1">
         <v>512</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="H31" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1024</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="H32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1">
+        <v>1024</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J32" s="1">
+    </row>
+    <row r="33" spans="2:11">
+      <c r="H33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J33" s="1">
         <v>2048</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="5" t="b">
+      <c r="K33" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D33" s="5" t="b">
+      <c r="D34" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="F34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="H34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J34" s="1">
-        <v>2</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="H35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="J35" s="1">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1001</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="H36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1">
+        <v>1001</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1002</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -2239,7 +2342,7 @@
         <v>110</v>
       </c>
       <c r="J37" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="38" spans="2:11">
@@ -2250,12 +2353,10 @@
         <v>112</v>
       </c>
       <c r="J38" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
       <c r="H39" s="1" t="s">
         <v>113</v>
       </c>
@@ -2263,10 +2364,12 @@
         <v>114</v>
       </c>
       <c r="J39" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="40" spans="2:11">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
       <c r="H40" s="1" t="s">
         <v>115</v>
       </c>
@@ -2274,7 +2377,7 @@
         <v>116</v>
       </c>
       <c r="J40" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2285,7 +2388,7 @@
         <v>118</v>
       </c>
       <c r="J41" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="42" spans="2:11">
@@ -2296,18 +2399,18 @@
         <v>120</v>
       </c>
       <c r="J42" s="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="H43" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J43" s="1">
         <v>1008</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="H43" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J43" s="5">
-        <v>2001</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -2318,7 +2421,7 @@
         <v>124</v>
       </c>
       <c r="J44" s="5">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -2329,18 +2432,18 @@
         <v>126</v>
       </c>
       <c r="J45" s="5">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="H46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J46" s="5">
         <v>2003</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="H46" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J46" s="5">
-        <v>2004</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2351,32 +2454,32 @@
         <v>130</v>
       </c>
       <c r="J47" s="5">
-        <v>2005</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>131</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="48" spans="2:11">
       <c r="H48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="J48" s="5">
+        <v>2005</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J48" s="5">
+    </row>
+    <row r="49" spans="8:10">
+      <c r="H49" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J49" s="5">
         <v>2006</v>
-      </c>
-    </row>
-    <row r="49" spans="8:10">
-      <c r="H49" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J49" s="5">
-        <v>2007</v>
       </c>
     </row>
     <row r="50" spans="8:10">
@@ -2387,18 +2490,18 @@
         <v>137</v>
       </c>
       <c r="J50" s="5">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="51" spans="8:10">
+      <c r="H51" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J51" s="5">
         <v>2008</v>
-      </c>
-    </row>
-    <row r="51" spans="8:10">
-      <c r="H51" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J51" s="1">
-        <v>3001</v>
       </c>
     </row>
     <row r="52" spans="8:10">
@@ -2409,7 +2512,7 @@
         <v>141</v>
       </c>
       <c r="J52" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="53" spans="8:10">
@@ -2420,7 +2523,7 @@
         <v>143</v>
       </c>
       <c r="J53" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="54" spans="8:10">
@@ -2431,7 +2534,7 @@
         <v>145</v>
       </c>
       <c r="J54" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="55" spans="8:10">
@@ -2442,7 +2545,7 @@
         <v>147</v>
       </c>
       <c r="J55" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="56" spans="8:10">
@@ -2453,7 +2556,7 @@
         <v>149</v>
       </c>
       <c r="J56" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="57" spans="8:10">
@@ -2464,7 +2567,7 @@
         <v>151</v>
       </c>
       <c r="J57" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="58" spans="8:10">
@@ -2475,7 +2578,7 @@
         <v>153</v>
       </c>
       <c r="J58" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="59" spans="8:10">
@@ -2486,7 +2589,7 @@
         <v>155</v>
       </c>
       <c r="J59" s="1">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="60" spans="8:10">
@@ -2497,33 +2600,33 @@
         <v>157</v>
       </c>
       <c r="J60" s="1">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="61" spans="8:10">
+      <c r="H61" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J61" s="1">
         <v>3010</v>
       </c>
     </row>
-    <row r="65" spans="2:10">
-      <c r="B65" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C65" s="5" t="b">
+    <row r="66" spans="2:11">
+      <c r="B66" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D65" s="5" t="b">
+      <c r="D66" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I65" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J65" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10">
       <c r="H66" s="1" t="s">
         <v>162</v>
       </c>
@@ -2531,10 +2634,10 @@
         <v>163</v>
       </c>
       <c r="J66" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
       <c r="H67" s="1" t="s">
         <v>164</v>
       </c>
@@ -2542,12 +2645,10 @@
         <v>165</v>
       </c>
       <c r="J67" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10">
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
       <c r="H68" s="1" t="s">
         <v>166</v>
       </c>
@@ -2555,10 +2656,12 @@
         <v>167</v>
       </c>
       <c r="J68" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
       <c r="H69" s="1" t="s">
         <v>168</v>
       </c>
@@ -2566,10 +2669,10 @@
         <v>169</v>
       </c>
       <c r="J69" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
       <c r="H70" s="1" t="s">
         <v>170</v>
       </c>
@@ -2577,10 +2680,10 @@
         <v>171</v>
       </c>
       <c r="J70" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
       <c r="H71" s="1" t="s">
         <v>172</v>
       </c>
@@ -2588,10 +2691,10 @@
         <v>173</v>
       </c>
       <c r="J71" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
       <c r="H72" s="1" t="s">
         <v>174</v>
       </c>
@@ -2599,12 +2702,10 @@
         <v>175</v>
       </c>
       <c r="J72" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10">
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
       <c r="H73" s="1" t="s">
         <v>176</v>
       </c>
@@ -2612,10 +2713,12 @@
         <v>177</v>
       </c>
       <c r="J73" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
       <c r="H74" s="1" t="s">
         <v>178</v>
       </c>
@@ -2623,58 +2726,240 @@
         <v>179</v>
       </c>
       <c r="J74" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="H75" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J75" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="2:9">
-      <c r="B98" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C98" s="5" t="b">
+    <row r="76" spans="2:11">
+      <c r="B76" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C76" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D98" s="5" t="b">
+      <c r="D76" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9">
-      <c r="H99" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="100" spans="2:9">
+      <c r="H76" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="H77" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="H78" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="H79" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J79" s="1">
+        <v>4</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="H80" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="H81" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J81" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C82" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="H83" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J83" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="H84" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J84" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="H85" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J85" s="1">
+        <v>4</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C86" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="H87" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J87" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C100" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D100" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="H100" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9">
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="I111" s="5"/>
-    </row>
-    <row r="112" spans="2:9">
-      <c r="I112" s="5"/>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8">
+      <c r="H101" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="H102" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="113" spans="3:9">
+      <c r="C113" s="5"/>
+      <c r="D113" s="5"/>
       <c r="I113" s="5"/>
     </row>
     <row r="114" spans="3:9">
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
+      <c r="I114" s="5"/>
     </row>
     <row r="115" spans="3:9">
       <c r="I115" s="5"/>
     </row>
+    <row r="116" spans="3:9">
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+    </row>
     <row r="117" spans="3:9">
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
       <c r="I117" s="5"/>
+    </row>
+    <row r="119" spans="3:9">
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="I119" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
